--- a/server/templates/price-update-template.xlsx
+++ b/server/templates/price-update-template.xlsx
@@ -12,12 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>کد محصول</t>
   </si>
   <si>
     <t>قیمت (تومان)</t>
+  </si>
+  <si>
+    <t>قیمت اعتباری (تومان)</t>
   </si>
   <si>
     <t>موجودی</t>
@@ -451,37 +454,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="18" customWidth="1"/>
+    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -495,36 +502,36 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>